--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -538,11 +538,11 @@
         <v>262</v>
       </c>
       <c r="H2" t="n">
-        <v>628043617747</v>
+        <v>628350577835</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35.548</t>
+          <t>35.566</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '11894668'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '13216296'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '437.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '96.04'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44804'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '70'}, {'stat_name': 'STR', 'stat_value': '24241'}, {'stat_name': 'DEX', 'stat_value': '2572'}, {'stat_name': 'INT', 'stat_value': '1491'}, {'stat_name': 'LUK', 'stat_value': '1526'}, {'stat_name': 'HP', 'stat_value': '71409'}, {'stat_name': 'MP', 'stat_value': '24528'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '90'}, {'stat_name': '攻擊速度', 'stat_value': '6'}, {'stat_name': '一般怪物傷害', 'stat_value': '32.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '47.50'}, {'stat_name': '攻擊力', 'stat_value': '2565'}, {'stat_name': '魔法攻擊力', 'stat_value': '743'}, {'stat_name': '戰鬥力', 'stat_value': '19178232'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
+          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '12738928'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '14154362'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '407.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '94.06'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44892'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '30'}, {'stat_name': 'STR', 'stat_value': '24241'}, {'stat_name': 'DEX', 'stat_value': '2792'}, {'stat_name': 'INT', 'stat_value': '1491'}, {'stat_name': 'LUK', 'stat_value': '1526'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '26359'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '70'}, {'stat_name': '攻擊速度', 'stat_value': '7'}, {'stat_name': '一般怪物傷害', 'stat_value': '12.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '35.00'}, {'stat_name': '攻擊力', 'stat_value': '2741'}, {'stat_name': '魔法攻擊力', 'stat_value': '731'}, {'stat_name': '戰鬥力', 'stat_value': '19771250'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -755,7 +755,7 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>559380</v>
+        <v>571230</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯I', 'skill_description': '[等級上限 : 4]\r\n艾拉諾斯跳躍並發射衝擊波攻擊周圍敵人。\n\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\n\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\n\n召喚艾拉諾斯70秒。\n艾拉諾斯跳躍：對最多10名敵人造成500%傷害，攻擊6次\n冷卻時間60秒\n艾拉諾斯成長時攻擊範圍與傷害增加。\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 4, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKA', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯II', 'skill_description': '[等級上限 : 4]\r\n艾拉諾斯啃咬前方，攻擊周圍敵人。\n\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\n\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\n\n召喚艾拉諾斯70秒。\n艾拉諾斯撕咬：對最多10名敵人造成550%傷害，攻擊6次\n冷卻時間60秒\n艾拉諾斯成長時攻擊範圍與傷害增加。\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 2, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKB', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯III', 'skill_description': '[等級上限 : 4]\r\n艾拉諾斯以鋒利的爪子攻擊周圍敵人。\n\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\n\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\n\n召喚艾拉諾斯70秒。\n艾拉諾斯利爪：對最多10名敵人造成600%傷害，攻擊6次\n冷卻時間60秒\n艾拉諾斯成長時攻擊範圍與傷害增加。\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKC', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯IV', 'skill_description': '[等級上限 : 4]\r\n艾拉諾斯猛烈咆哮，攻擊周圍敵人。\n\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\n\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\n\n召喚艾拉諾斯70秒。\n艾拉諾斯咆哮：對最多10名敵人造成650%傷害，攻擊6次\n冷卻時間60秒\n艾拉諾斯成長時攻擊範圍與傷害增加。\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 4, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKD', 'skill_effect_next': None}, {'skill_name': '幻影魔法', 'skill_description': '[等級上限 : 1]\r\n由記憶與回憶的幻影交織而成的神祕魔法。', 'skill_level': 1, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKF', 'skill_effect_next': None}, {'skill_name': '咆哮的艾拉諾斯', 'skill_description': '[最高等級：1]\n每當消滅等級範圍怪物時可累積計量表，\n當計量表全滿時，即可發動&lt;咆哮的艾拉諾斯&gt;。\n\n每日&lt;咆哮的艾拉諾斯&gt;發動次數達到20次時\n結束。\n\n活動期間結束後將無法使用。\n\n - 變更開關\n右擊新手技能欄&lt;咆哮的艾拉諾斯&gt;技能\n - 變更自動/手動\n右擊UI的&lt;咆哮的艾拉諾斯&gt;技能\n', 'skill_level': 1, 'skill_effect': '\n\n&lt;咆哮的艾拉諾斯II&gt;最多對15名敵人以3000%傷害攻擊1次的\n爆炸發動6次的技能發動6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEE', 'skill_effect_next': None}, {'skill_name': '古代力量', 'skill_description': '[等級上限 : 1]\r\n隨著透過調查逐步找回力量，將會越來越強。', 'skill_level': 1, 'skill_effect': '攻擊力/魔力增加 30\r\n攻擊BOSS怪物時傷害增加40%\r\n無視怪物防禦率增加40%\r\nBuff持續時間增加20%\r\n攻擊一般怪物時傷害增加 20%\r\n經驗值獲得量增加12.5%\r\n消滅BOSS怪物時獲得的靈魂艾爾達氣息增加100%\r\n從怪物公園退場時獲得的經驗值增加50%\r\n完成奧術之河每日任務時，獲得經驗值增加50%、獲得符文增加20個\r\n完成格蘭蒂斯每日任務時，增加50%獲得的經驗值、9個獲得的符文\r\n真實之力增加40\r\n從怪物公園退場時獲得的經驗值增加30%\r\n智慧餘響經驗值增加200%\r\n消滅BOSS怪物時，獲得的靈魂艾爾達氣息增加40%\r\n完成奧術之河每日任務時，增加20%獲得的經驗值、4個獲得的符文\r\n完成格蘭蒂斯每日任務時，增加20%獲得的經驗值、3個獲得的符文\r\n狩獵場獲得靈魂艾爾達氣息100%增加\r\n寶藏獵人經驗值獲得量100%增加\r\n攻擊BOSS怪物時傷害增加10%\r\n史詩副本基本經驗值獎勵獲得量150%增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEH', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '遊樂場吉祥物 Lv.1', 'skill_description': '[等級上限 : 1]\r\n利用遊樂場吉祥物的力量，讓自己的攻擊力和魔力各增加8。', 'skill_level': 1, 'skill_effect': '增加攻擊力 8、魔力 8', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHOIOF', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '特別課程', 'skill_description': '[等級上限 : 1]\r\n這是在楓之谷學院進行中的武公與艾畢奈亞的課程。', 'skill_level': 1, 'skill_effect': '增加攻擊BOSS怪物時傷害 20%\r\n無視怪物防禦率增加10%\r\n從怪物公園退場時獲得的經驗值增加20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHNJFD', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[{'skill_name': '連接繩索', 'skill_description': '[等級上限 : 30]\r\n將鐵鍊拋向天空，快速移動。', 'skill_level': 19, 'skill_effect': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力19]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMA', 'skill_effect_next': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力20]'}, {'skill_name': '實用的時空門', 'skill_description': '[等級上限 : 30]\r\n形成可通往最近村莊的傳送點。門消失之前可以多次進出，在傳送點上按 ↑ 鍵移動。', 'skill_level': 10, 'skill_effect': '消耗100 HP，維持傳送點50秒\n冷卻時間為130秒\n[被動效果：全屬性增加2]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMB', 'skill_effect_next': '消耗100 HP，維持傳送點52秒\n冷卻時間為130秒\n[被動效果：全屬性增加3]'}, {'skill_name': '實用的會心之眼', 'skill_description': '[等級上限 : 30]\r\n賦予自己能找出敵人的弱點造成致命傷的能力。不能跟會心之眼重複使用。', 'skill_level': 25, 'skill_effect': '消耗HP 100，在255秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMC', 'skill_effect_next': '消耗HP 100，在258秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 6增加]'}, {'skill_name': '實用的神聖之火', 'skill_description': '[等級上限 : 30]\r\n最大HP與最大MP的量增加。不會與神聖之火重複使用。', 'skill_level': 21, 'skill_effect': '消耗HP 100，在243秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMD', 'skill_effect_next': '消耗HP 100，在246秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]'}, {'skill_name': '實用的戰鬥命令', 'skill_description': '[等級上限 : 30]\r\n一定時間內提升自身的所有技能等級。限於4轉技能可以增加到最大等級以上，其他技能只能提高到最大等級為止。\n部分例外的特別技能和初心者技能、戰鬥命令、實用的戰鬥命令、超技能、5轉、6轉技能的等級是無法提高技能等級。\n無法與戰鬥命令重複使用。', 'skill_level': 22, 'skill_effect': '消耗HP 100，在246秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBME', 'skill_effect_next': '消耗HP 100，在249秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]'}, {'skill_name': '實用的進階祝福', 'skill_description': '[等級上限 : 30]\r\n增加攻擊力、魔力、防禦力、最大HP、最大MP。\n祝福、進階祝福、實用的進階祝福中，僅套用較高數值的效果。', 'skill_level': 15, 'skill_effect': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加3]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMF', 'skill_effect_next': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加4]'}, {'skill_name': '實用的最終極速', 'skill_description': '[等級上限 : 30]\r\n使自己的攻擊速度額外增加1階段。最終極速和實用的最終極速中，僅套用較高數值的效果。', 'skill_level': 22, 'skill_effect': '攻擊速度增加1階段\n[被動效果：全屬性增加5]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMG', 'skill_effect_next': '攻擊速度增加1階段\n[被動效果：全屬性增加5]'}, {'skill_name': '瞬移', 'skill_description': '[等級上限 : 30]\r\n瞬間移動到地圖上隨機的位置。在空中按壓按鍵時，會在一定時間內漂浮且慢速移動來代替瞬間移動。', 'skill_level': 22, 'skill_effect': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 22增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMH', 'skill_effect_next': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 23增加]'}, {'skill_name': '艾爾達斯的新星', 'skill_description': '[等級上限 : 30]\r\n收集自己周圍的艾爾達斯後朝敵人引爆攻擊。被攻擊的敵人體內艾爾達紊亂，陷入無法行動狀態。\n艾爾達新星可在其他技能施放中使用，並可對攻擊無視與攻擊反射狀態的敵人造成傷害。', 'skill_level': 30, 'skill_effect': '消耗100 HP，對最多10名的敵人以330%的傷害攻擊5次，並進入無法行動狀態10秒\n依照利用艾爾達斯的超新星對敵人造成的傷害而增加無法行動的持續時間，最多增加100%\n冷卻時間 100秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMI', 'skill_effect_next': None}, {'skill_name': '艾爾達斯的意志', 'skill_description': '[等級上限 : 30]\r\n集中精神，以解除狀態異常。使用後，在3秒內對狀態異常免疫。但部分異常狀態效果不適用。\n艾爾達斯的意志在使用其他技能時仍可使用。', 'skill_level': 16, 'skill_effect': '消耗100 HP，冷卻時間400秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMJ', 'skill_effect_next': '消耗100 HP，冷卻時間395秒'}, {'skill_name': '實用的祈禱', 'skill_description': '[等級上限 : 30]\r\n一定時間內狩獵怪物時，可獲得更多的經驗值和道具。不能跟神聖祈禱重複使用。', 'skill_level': 19, 'skill_effect': '消耗HP 100，237秒間獲得經驗值增加29%，掉寶率增加20%\n冷卻時間 180秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBOA', 'skill_effect_next': '消耗HP 100，240秒間獲得經驗值增加30%，掉寶率增加20%\n冷卻時間 180秒'}, {'skill_name': '艾爾達斯的降臨', 'skill_description': '[等級上限 : 30]\r\n釋放濃縮的艾爾達攻擊周圍敵人。\n與方向鍵下同時使用時可召喚純淨艾爾達匯聚的物件艾爾達噴泉。\n使用自訂指令時可不輸入方向鍵僅以技能鍵召喚艾爾達噴泉。\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影侍從、祝雷、藍血、虛擬投影時，攻擊次數增加效果將改為相同效果的最終傷害增加。\n指令開關：滑鼠右鍵', 'skill_level': 18, 'skill_effect': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPG', 'skill_effect_next': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間'}, {'skill_name': '魔法迴路效能全開', 'skill_description': '[等級上限 : 30]\r\n魔力翅膀張開到最大將魔法迴路啟動到極限。', 'skill_level': 30, 'skill_effect': '消耗1000 MP，在60秒內，傷害增加45%\n使用攻擊技能時，每4秒額外消耗150MP，並發動魔力暴風最多對6名敵人造成1100%傷害攻擊3次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPH', 'skill_effect_next': None}, {'skill_name': '蜘蛛之鏡', 'skill_description': '[等級上限 : 30]\r\n利用威爾的艾爾達斯來崩壞空間，並把鏡面世界和現實世界連接後，把鏡面裡的蜘蛛具現在現實空間中。鏡面的蜘蛛攻擊處於反射狀態的敵人時，也不會使自己受傷。', 'skill_level': 1, 'skill_effect': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPJ', 'skill_effect_next': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒'}, {'skill_name': '格蘭蒂斯女神的祝福', 'skill_description': '[等級上限 : 30]\r\n依據不同種族展現相異樣貌的格蘭蒂斯女神，賜予與種族相符的祝福。受冷卻時間減少效果影響。', 'skill_level': 30, 'skill_effect': 'HP 100消耗，持續40秒\n超新星：使用技能時55%機率不受冷卻時間影響，最多6次不受影響\n傷害35%增加\n每個龍能球能量階段使凱撒的傷害追加增加11%\n雷普：將除武器外的裝備中，不使用屬性的攻擊力/魔力100%轉換為使用屬性。但不適用套裝效果，僅能轉換武器純攻擊力/魔力的150%為使用屬性\n攻擊力與魔力增加100\n阿尼瑪：傷害增加40%\n虎影的符籍與卷軸道力補充量增加75%，菈菈在龍脈迴響觸發時最終傷害增幅為11%，蓮的梅花劍絕技、亡魂劍絕技、蒼龍破天劍的最終傷害增加15%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBIG', 'skill_effect_next': None}, {'skill_name': '烈陽印記', 'skill_description': '[等級上限 : 30]\r\n利用米特拉的力量釋出太陽的熱氣後，具現出火焰的憤怒。火焰的紋樣即使對反射攻擊狀態的敵人進行攻擊也不會受到傷害。', 'skill_level': 2, 'skill_effect': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBJJ', 'skill_effect_next': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒'}, {'skill_name': '實用的神聖之泉', 'skill_description': '[等級上限 : 30]\r\n召喚神聖的噴泉，用神聖的力量恢復隊員的HP。不死狀態的隊員也可使用，靠近噴泉並按下向上方向鍵即可回復HP。\n包含自身在內的隊員所使用的神聖之泉及實用的神聖之泉，在地圖內只能存在一個。\n實用的神聖之泉在持續時間結束前消失時，會留下神聖之痕。在存在神聖之泉以及除自身外隊員的實用的神聖之泉及神聖之痕的地圖中無法使用。\n不受再使用冷卻時間重置、回復技能效率增加、增加召喚獸持續時間效果影響，且無法在傳送點附近召喚。', 'skill_level': 19, 'skill_effect': '消耗100 HP，持續49秒。使用時將恢復20%HP，共可使用14次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為71秒\n[被動效果：全屬性增加4]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBFH', 'skill_effect_next': '消耗100 HP，持續50秒。使用時將恢復25%HP，共可使用15次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為70秒\n[被動效果：全屬性增加4]'}, {'skill_name': '碎片/奇蹟強化', 'skill_description': '[等級上限 : 60]\r\n強化碎片/奇蹟。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '碎片/奇蹟的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAII', 'skill_effect_next': None}, {'skill_name': '行星強化', 'skill_description': '[等級上限 : 60]\r\n強化行星。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '行星的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIG', 'skill_effect_next': None}, {'skill_name': '閃擊強化', 'skill_description': '[等級上限 : 60]\r\n強化閃擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '閃擊的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIH', 'skill_effect_next': None}, {'skill_name': '刺擊強化', 'skill_description': '[等級上限 : 60]\r\n強化刺擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '刺擊的最終傷害增加300%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJA', 'skill_effect_next': None}, {'skill_name': '十字斬強化', 'skill_description': '[等級上限 : 60]\r\n強化十字斬。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '十字斬的最終傷害增加180%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJB', 'skill_effect_next': None}, {'skill_name': '穿刺強化', 'skill_description': '[等級上限 : 60]\r\n強化穿刺。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '穿刺的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJC', 'skill_effect_next': None}, {'skill_name': '魔劍共鳴強化', 'skill_description': '[等級上限 : 60]\r\n強化魔劍共鳴。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔劍共鳴的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJD', 'skill_effect_next': None}, {'skill_name': '魔力爆裂強化', 'skill_description': '[等級上限 : 60]\r\n強化魔力爆裂。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔力爆裂的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJE', 'skill_effect_next': None}, {'skill_name': '創造強化', 'skill_description': '[等級上限 : 60]\r\n強化創造。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '創造的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJF', 'skill_effect_next': None}, {'skill_name': '回歸強化', 'skill_description': '[等級上限 : 60]\r\n強化回歸。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率強化20%', 'skill_level': 60, 'skill_effect': '回歸的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJG', 'skill_effect_next': None}, {'skill_name': '劍域強化', 'skill_description': '[等級上限 : 60]\r\n強化劍域。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '劍域的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJH', 'skill_effect_next': None}, {'skill_name': '踐踏強化', 'skill_description': '[等級上限 : 60]\r\n強化踐踏。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '踐踏的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJI', 'skill_effect_next': None}, {'skill_name': '切割強化', 'skill_description': '[等級上限 : 60]\r\n強化切割。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '切割的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJJ', 'skill_effect_next': None}, {'skill_name': '追蹤強化', 'skill_description': '[等級上限 : 60]\r\n強化追蹤。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '追蹤的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKA', 'skill_effect_next': None}, {'skill_name': '死亡標記強化', 'skill_description': '[等級上限 : 60]\r\n強化死亡標記。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '死亡標記的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKB', 'skill_effect_next': None}, {'skill_name': '綻放強化', 'skill_description': '[等級上限 : 60]\r\n強化綻放。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '綻放的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKC', 'skill_effect_next': None}, {'skill_name': '狂風強化', 'skill_description': '[等級上限 : 60]\r\n強化狂風。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '狂風的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKD', 'skill_effect_next': None}, {'skill_name': '幻靈武具', 'skill_description': '[等級上限 : 30]\r\n將部分生命力賦予武器，發揮強大的力量。', 'skill_level': 30, 'skill_effect': '消耗100 HP，130秒內無視怪物防禦率 16%，最終傷害值增加6% 。\n每5秒使用自己的攻擊技能時，發射鬥氣波動攻擊敵人，最多對10名敵人造成1100%傷害6次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBMA', 'skill_effect_next': None}, {'skill_name': '鋼鐵之軀', 'skill_description': '[等級上限 : 30]\r\n肉體變成和鋼鐵一樣，不會受敵人的攻擊彈開。', 'skill_level': 30, 'skill_effect': '消耗100 HP，在18秒內，不會被任何攻擊擊退，並提升狀態異常抗性80\n冷卻時間120秒\n[被動效果：力量增加30、最大HP增加1500]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBKG', 'skill_effect_next': None}, {'skill_name': '毀滅', 'skill_description': '[等級上限 : 30]\r\n召喚古代滅亡之劍讓四周崩毀。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害。', 'skill_level': 30, 'skill_effect': '消耗MP1000，最多攻擊15名敵人\n召喚後，發動以1012%傷害攻擊6次的攻擊12次\n召喚後插上劍，發動以1485%傷害攻擊9次的攻擊8次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMF', 'skill_effect_next': None}, {'skill_name': '無限', 'skill_description': '[等級上限 : 30]\r\n創造一個空間，讓無數的乙太之劍生成。乙太之劍只會在阿戴爾附近追擊敵人，當劍和阿戴爾之間的距離變遠，劍會移動到阿戴爾附近追擊新敵人。\n以無限指令創造出來的乙太之劍會進行回歸；不套用爆裂，只套用死亡標記。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害，只有在阿戴爾處於戰鬥狀態時才會追擊敵人。\r\n所需技能：死亡標記 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP1000，在進行施展及解除動作時無敵\n存在20秒，創造18把乙太之劍，可以770%傷害攻擊2次\n攻擊命中時以5%機率形成乙太結晶\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMI', 'skill_effect_next': None}, {'skill_name': '復原', 'skill_description': '[等級上限 : 30]\r\n暫時修復燒焦的魔力迴路，讓過去的魔力之翼復活。\n復原的攻擊可無視打擊，並且可對反射攻勢狀態的敵人造成傷害，再次使用技能時會立刻消失。\r\n所需技能：高潔精神 10等級以上', 'skill_level': 30, 'skill_effect': '施放及施放後，每秒消耗最大MP的2%\n20秒內，傷害增加45%、乙太獲得量增加80%、可聽從追蹤命令的乙太之劍增加2把。施展時，無論持有多少乙太之劍，立即命令2把乙太之劍\n每隔一定時間展開魔力翅膀，最多對6名敵人造成1980%傷害攻擊3次，恢復包含自身在內的隊員最大HP的10.5%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMJ', 'skill_effect_next': None}, {'skill_name': '乙太風暴', 'skill_description': '[等級上限 : 30]\r\n讓下達追蹤命令的所有乙太之劍在自身周圍有如暴風般地移動。以追蹤追擊敵人的乙太之劍數量比例，在自身周圍產生幻影移動。暴風攻擊即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。再次使用技能時可立即結束。\r\n所需技能：回歸 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP500，14秒內每隔一段時間會最多向7名敵人以869%傷害自動攻擊2次\n施展時下達命令的乙太之劍每超出1雙，攻擊次數增加2次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAPG', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '連接繩索', 'skill_description': '[等級上限 : 30]\r\n將鐵鍊拋向天空，快速移動。', 'skill_level': 19, 'skill_effect': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力19]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMA', 'skill_effect_next': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力20]'}, {'skill_name': '實用的時空門', 'skill_description': '[等級上限 : 30]\r\n形成可通往最近村莊的傳送點。門消失之前可以多次進出，在傳送點上按 ↑ 鍵移動。', 'skill_level': 10, 'skill_effect': '消耗100 HP，維持傳送點50秒\n冷卻時間為130秒\n[被動效果：全屬性增加2]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMB', 'skill_effect_next': '消耗100 HP，維持傳送點52秒\n冷卻時間為130秒\n[被動效果：全屬性增加3]'}, {'skill_name': '實用的會心之眼', 'skill_description': '[等級上限 : 30]\r\n賦予自己能找出敵人的弱點造成致命傷的能力。不能跟會心之眼重複使用。', 'skill_level': 25, 'skill_effect': '消耗HP 100，在255秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMC', 'skill_effect_next': '消耗HP 100，在258秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 6增加]'}, {'skill_name': '實用的神聖之火', 'skill_description': '[等級上限 : 30]\r\n最大HP與最大MP的量增加。不會與神聖之火重複使用。', 'skill_level': 21, 'skill_effect': '消耗HP 100，在243秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMD', 'skill_effect_next': '消耗HP 100，在246秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]'}, {'skill_name': '實用的戰鬥命令', 'skill_description': '[等級上限 : 30]\r\n一定時間內提升自身的所有技能等級。限於4轉技能可以增加到最大等級以上，其他技能只能提高到最大等級為止。\n部分例外的特別技能和初心者技能、戰鬥命令、實用的戰鬥命令、超技能、5轉、6轉技能的等級是無法提高技能等級。\n無法與戰鬥命令重複使用。', 'skill_level': 22, 'skill_effect': '消耗HP 100，在246秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBME', 'skill_effect_next': '消耗HP 100，在249秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]'}, {'skill_name': '實用的進階祝福', 'skill_description': '[等級上限 : 30]\r\n增加攻擊力、魔力、防禦力、最大HP、最大MP。\n祝福、進階祝福、實用的進階祝福中，僅套用較高數值的效果。', 'skill_level': 15, 'skill_effect': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加3]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMF', 'skill_effect_next': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加4]'}, {'skill_name': '實用的最終極速', 'skill_description': '[等級上限 : 30]\r\n使自己的攻擊速度額外增加1階段。最終極速和實用的最終極速中，僅套用較高數值的效果。', 'skill_level': 22, 'skill_effect': '攻擊速度增加1階段\n[被動效果：全屬性增加5]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMG', 'skill_effect_next': '攻擊速度增加1階段\n[被動效果：全屬性增加5]'}, {'skill_name': '瞬移', 'skill_description': '[等級上限 : 30]\r\n瞬間移動到地圖上隨機的位置。在空中按壓按鍵時，會在一定時間內漂浮且慢速移動來代替瞬間移動。', 'skill_level': 22, 'skill_effect': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 22增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMH', 'skill_effect_next': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 23增加]'}, {'skill_name': '艾爾達斯的新星', 'skill_description': '[等級上限 : 30]\r\n收集自己周圍的艾爾達斯後朝敵人引爆攻擊。被攻擊的敵人體內艾爾達紊亂，陷入無法行動狀態。\n艾爾達新星可在其他技能施放中使用，並可對攻擊無視與攻擊反射狀態的敵人造成傷害。', 'skill_level': 30, 'skill_effect': '消耗100 HP，對最多10名的敵人以330%的傷害攻擊5次，並進入無法行動狀態10秒\n依照利用艾爾達斯的超新星對敵人造成的傷害而增加無法行動的持續時間，最多增加100%\n冷卻時間 100秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMI', 'skill_effect_next': None}, {'skill_name': '艾爾達斯的意志', 'skill_description': '[等級上限 : 30]\r\n集中精神，以解除狀態異常。使用後，在3秒內對狀態異常免疫。但部分異常狀態效果不適用。\n艾爾達斯的意志在使用其他技能時仍可使用。', 'skill_level': 16, 'skill_effect': '消耗100 HP，冷卻時間400秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMJ', 'skill_effect_next': '消耗100 HP，冷卻時間395秒'}, {'skill_name': '實用的祈禱', 'skill_description': '[等級上限 : 30]\r\n一定時間內狩獵怪物時，可獲得更多的經驗值和道具。不能跟神聖祈禱重複使用。', 'skill_level': 19, 'skill_effect': '消耗HP 100，237秒間獲得經驗值增加29%，掉寶率增加20%\n冷卻時間 180秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBOA', 'skill_effect_next': '消耗HP 100，240秒間獲得經驗值增加30%，掉寶率增加20%\n冷卻時間 180秒'}, {'skill_name': '艾爾達斯的降臨', 'skill_description': '[等級上限 : 30]\r\n釋放濃縮的艾爾達攻擊周圍敵人。\n與方向鍵下同時使用時可召喚純淨艾爾達匯聚的物件艾爾達噴泉。\n使用自訂指令時可不輸入方向鍵僅以技能鍵召喚艾爾達噴泉。\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影侍從、祝雷、藍血、虛擬投影時，攻擊次數增加效果將改為相同效果的最終傷害增加。\n指令開關：滑鼠右鍵', 'skill_level': 18, 'skill_effect': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPG', 'skill_effect_next': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間'}, {'skill_name': '魔法迴路效能全開', 'skill_description': '[等級上限 : 30]\r\n魔力翅膀張開到最大將魔法迴路啟動到極限。', 'skill_level': 30, 'skill_effect': '消耗1000 MP，在60秒內，傷害增加45%\n使用攻擊技能時，每4秒額外消耗150MP，並發動魔力暴風最多對6名敵人造成1100%傷害攻擊3次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPH', 'skill_effect_next': None}, {'skill_name': '蜘蛛之鏡', 'skill_description': '[等級上限 : 30]\r\n利用威爾的艾爾達斯來崩壞空間，並把鏡面世界和現實世界連接後，把鏡面裡的蜘蛛具現在現實空間中。鏡面的蜘蛛攻擊處於反射狀態的敵人時，也不會使自己受傷。', 'skill_level': 1, 'skill_effect': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPJ', 'skill_effect_next': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒'}, {'skill_name': '格蘭蒂斯女神的祝福', 'skill_description': '[等級上限 : 30]\r\n依據不同種族展現相異樣貌的格蘭蒂斯女神，賜予與種族相符的祝福。受冷卻時間減少效果影響。', 'skill_level': 30, 'skill_effect': 'HP 100消耗，持續40秒\n超新星：使用技能時55%機率不受冷卻時間影響，最多6次不受影響\n傷害35%增加\n每個龍能球能量階段使凱撒的傷害追加增加11%\n雷普：將除武器外的裝備中，不使用屬性的攻擊力/魔力100%轉換為使用屬性。但不適用套裝效果，僅能轉換武器純攻擊力/魔力的150%為使用屬性\n攻擊力與魔力增加100\n阿尼瑪：傷害增加40%\n虎影的符籍與卷軸道力補充量增加75%，菈菈在龍脈迴響觸發時最終傷害增幅為11%，蓮的梅花劍絕技、亡魂劍絕技、蒼龍破天劍的最終傷害增加15%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBIG', 'skill_effect_next': None}, {'skill_name': '烈陽印記', 'skill_description': '[等級上限 : 30]\r\n利用米特拉的力量釋出太陽的熱氣後，具現出火焰的憤怒。火焰的紋樣即使對反射攻擊狀態的敵人進行攻擊也不會受到傷害。', 'skill_level': 2, 'skill_effect': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBJJ', 'skill_effect_next': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒'}, {'skill_name': '實用的神聖之泉', 'skill_description': '[等級上限 : 30]\r\n召喚神聖的噴泉，用神聖的力量恢復隊員的HP。不死狀態的隊員也可使用，靠近噴泉並按下向上方向鍵即可回復HP。\n包含自身在內的隊員所使用的神聖之泉及實用的神聖之泉，在地圖內只能存在一個。\n實用的神聖之泉在持續時間結束前消失時，會留下神聖之痕。在存在神聖之泉以及除自身外隊員的實用的神聖之泉及神聖之痕的地圖中無法使用。\n不受再使用冷卻時間重置、回復技能效率增加、增加召喚獸持續時間效果影響，且無法在傳送點附近召喚。', 'skill_level': 19, 'skill_effect': '消耗100 HP，持續49秒。使用時將恢復20%HP，共可使用14次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為71秒\n[被動效果：全屬性增加4]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBFH', 'skill_effect_next': '消耗100 HP，持續50秒。使用時將恢復25%HP，共可使用15次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為70秒\n[被動效果：全屬性增加4]'}, {'skill_name': '行星強化', 'skill_description': '[等級上限 : 60]\r\n強化行星。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '行星的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIG', 'skill_effect_next': None}, {'skill_name': '碎片/奇蹟強化', 'skill_description': '[等級上限 : 60]\r\n強化碎片/奇蹟。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '碎片/奇蹟的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAII', 'skill_effect_next': None}, {'skill_name': '閃擊強化', 'skill_description': '[等級上限 : 60]\r\n強化閃擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '閃擊的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIH', 'skill_effect_next': None}, {'skill_name': '刺擊強化', 'skill_description': '[等級上限 : 60]\r\n強化刺擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '刺擊的最終傷害增加300%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJA', 'skill_effect_next': None}, {'skill_name': '穿刺強化', 'skill_description': '[等級上限 : 60]\r\n強化穿刺。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '穿刺的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJC', 'skill_effect_next': None}, {'skill_name': '魔劍共鳴強化', 'skill_description': '[等級上限 : 60]\r\n強化魔劍共鳴。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔劍共鳴的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJD', 'skill_effect_next': None}, {'skill_name': '創造強化', 'skill_description': '[等級上限 : 60]\r\n強化創造。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '創造的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJF', 'skill_effect_next': None}, {'skill_name': '十字斬強化', 'skill_description': '[等級上限 : 60]\r\n強化十字斬。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '十字斬的最終傷害增加180%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJB', 'skill_effect_next': None}, {'skill_name': '追蹤強化', 'skill_description': '[等級上限 : 60]\r\n強化追蹤。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '追蹤的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKA', 'skill_effect_next': None}, {'skill_name': '回歸強化', 'skill_description': '[等級上限 : 60]\r\n強化回歸。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率強化20%', 'skill_level': 60, 'skill_effect': '回歸的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJG', 'skill_effect_next': None}, {'skill_name': '劍域強化', 'skill_description': '[等級上限 : 60]\r\n強化劍域。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '劍域的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJH', 'skill_effect_next': None}, {'skill_name': '切割強化', 'skill_description': '[等級上限 : 60]\r\n強化切割。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '切割的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJJ', 'skill_effect_next': None}, {'skill_name': '綻放強化', 'skill_description': '[等級上限 : 60]\r\n強化綻放。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '綻放的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKC', 'skill_effect_next': None}, {'skill_name': '死亡標記強化', 'skill_description': '[等級上限 : 60]\r\n強化死亡標記。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '死亡標記的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKB', 'skill_effect_next': None}, {'skill_name': '踐踏強化', 'skill_description': '[等級上限 : 60]\r\n強化踐踏。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '踐踏的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJI', 'skill_effect_next': None}, {'skill_name': '狂風強化', 'skill_description': '[等級上限 : 60]\r\n強化狂風。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '狂風的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKD', 'skill_effect_next': None}, {'skill_name': '魔力爆裂強化', 'skill_description': '[等級上限 : 60]\r\n強化魔力爆裂。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔力爆裂的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJE', 'skill_effect_next': None}, {'skill_name': '幻靈武具', 'skill_description': '[等級上限 : 30]\r\n將部分生命力賦予武器，發揮強大的力量。', 'skill_level': 30, 'skill_effect': '消耗100 HP，130秒內無視怪物防禦率 16%，最終傷害值增加6% 。\n每5秒使用自己的攻擊技能時，發射鬥氣波動攻擊敵人，最多對10名敵人造成1100%傷害6次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBMA', 'skill_effect_next': None}, {'skill_name': '鋼鐵之軀', 'skill_description': '[等級上限 : 30]\r\n肉體變成和鋼鐵一樣，不會受敵人的攻擊彈開。', 'skill_level': 30, 'skill_effect': '消耗100 HP，在18秒內，不會被任何攻擊擊退，並提升狀態異常抗性80\n冷卻時間120秒\n[被動效果：力量增加30、最大HP增加1500]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBKG', 'skill_effect_next': None}, {'skill_name': '毀滅', 'skill_description': '[等級上限 : 30]\r\n召喚古代滅亡之劍讓四周崩毀。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害。', 'skill_level': 30, 'skill_effect': '消耗MP1000，最多攻擊15名敵人\n召喚後，發動以1012%傷害攻擊6次的攻擊12次\n召喚後插上劍，發動以1485%傷害攻擊9次的攻擊8次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMF', 'skill_effect_next': None}, {'skill_name': '無限', 'skill_description': '[等級上限 : 30]\r\n創造一個空間，讓無數的乙太之劍生成。乙太之劍只會在阿戴爾附近追擊敵人，當劍和阿戴爾之間的距離變遠，劍會移動到阿戴爾附近追擊新敵人。\n以無限指令創造出來的乙太之劍會進行回歸；不套用爆裂，只套用死亡標記。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害，只有在阿戴爾處於戰鬥狀態時才會追擊敵人。\r\n所需技能：死亡標記 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP1000，在進行施展及解除動作時無敵\n存在20秒，創造18把乙太之劍，可以770%傷害攻擊2次\n攻擊命中時以5%機率形成乙太結晶\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMI', 'skill_effect_next': None}, {'skill_name': '復原', 'skill_description': '[等級上限 : 30]\r\n暫時修復燒焦的魔力迴路，讓過去的魔力之翼復活。\n復原的攻擊可無視打擊，並且可對反射攻勢狀態的敵人造成傷害，再次使用技能時會立刻消失。\r\n所需技能：高潔精神 10等級以上', 'skill_level': 30, 'skill_effect': '施放及施放後，每秒消耗最大MP的2%\n20秒內，傷害增加45%、乙太獲得量增加80%、可聽從追蹤命令的乙太之劍增加2把。施展時，無論持有多少乙太之劍，立即命令2把乙太之劍\n每隔一定時間展開魔力翅膀，最多對6名敵人造成1980%傷害攻擊3次，恢復包含自身在內的隊員最大HP的10.5%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMJ', 'skill_effect_next': None}, {'skill_name': '乙太風暴', 'skill_description': '[等級上限 : 30]\r\n讓下達追蹤命令的所有乙太之劍在自身周圍有如暴風般地移動。以追蹤追擊敵人的乙太之劍數量比例，在自身周圍產生幻影移動。暴風攻擊即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。再次使用技能時可立即結束。\r\n所需技能：回歸 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP500，14秒內每隔一段時間會最多向7名敵人以869%傷害自動攻擊2次\n施展時下達命令的乙太之劍每超出1雙，攻擊次數增加2次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAPG', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1487,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'MaxHP +300', 'potential_option_2': '被打擊後無敵時間 +2秒', 'potential_option_3': '被擊中時有5% 機率無視 20% 傷害', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000'</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'DEX +13%', 'potential_option_2': 'DEX +16', 'potential_option_3': 'MaxMP +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_power'</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'MaxHP +300', 'potential_option_2': '被打擊後無敵時間 +2秒', 'potential_option_3': '被擊中時有5% 機率無視 20% 傷害', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000'</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'DEX +13%', 'potential_option_2': 'DEX +16', 'potential_option_3': 'MaxMP +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_power'</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '戒指', 'item_equipment_slot': '戒指4', 'item_name': '銀花戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_description': None, 'item_shape_name': '銀花戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_gender': None, 'item_total_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 110}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +12', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '3', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'MaxHP +300', 'potential_option_2': '被打擊後無敵時間 +2秒', 'potential_option_3': '被擊中時有5% 機率無視 20% 傷害', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damag</t>
+          <t>[{'item_equipment_part': '戒指', 'item_equipment_slot': '戒指4', 'item_name': '銀花戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_description': None, 'item_shape_name': '銀花戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_gender': None, 'item_total_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 110}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +12', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '3', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'DEX +13%', 'potential_option_2': 'DEX +16', 'potential_option_3': 'MaxMP +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'MaxHP +300', 'potential_option_2': '被打擊後無敵時間 +2秒', 'potential_option_3': '被擊中時有5% 機率無視 20% 傷害', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000'</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'DEX +13%', 'potential_option_2': 'DEX +16', 'potential_option_3': 'MaxMP +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_power'</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '12738928'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '14154362'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '407.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '94.06'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44892'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '30'}, {'stat_name': 'STR', 'stat_value': '24241'}, {'stat_name': 'DEX', 'stat_value': '2792'}, {'stat_name': 'INT', 'stat_value': '1491'}, {'stat_name': 'LUK', 'stat_value': '1526'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '26359'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '70'}, {'stat_name': '攻擊速度', 'stat_value': '7'}, {'stat_name': '一般怪物傷害', 'stat_value': '12.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '35.00'}, {'stat_name': '攻擊力', 'stat_value': '2741'}, {'stat_name': '魔法攻擊力', 'stat_value': '731'}, {'stat_name': '戰鬥力', 'stat_value': '19771250'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
+          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '11702524'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '13002802'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '407.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '94.06'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44892'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '30'}, {'stat_name': 'STR', 'stat_value': '24241'}, {'stat_name': 'DEX', 'stat_value': '2792'}, {'stat_name': 'INT', 'stat_value': '1491'}, {'stat_name': 'LUK', 'stat_value': '1526'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '26359'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '70'}, {'stat_name': '攻擊速度', 'stat_value': '7'}, {'stat_name': '一般怪物傷害', 'stat_value': '12.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '35.00'}, {'stat_name': '攻擊力', 'stat_value': '2518'}, {'stat_name': '魔法攻擊力', 'stat_value': '712'}, {'stat_name': '戰鬥力', 'stat_value': '17771467'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -943,7 +943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '遊樂場吉祥物 Lv.1', 'skill_description': '[等級上限 : 1]\r\n利用遊樂場吉祥物的力量，讓自己的攻擊力和魔力各增加8。', 'skill_level': 1, 'skill_effect': '增加攻擊力 8、魔力 8', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHOIOF', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '特別課程', 'skill_description': '[等級上限 : 1]\r\n這是在楓之谷學院進行中的武公與艾畢奈亞的課程。', 'skill_level': 1, 'skill_effect': '增加攻擊BOSS怪物時傷害 20%\r\n無視怪物防禦率增加10%\r\n從怪物公園退場時獲得的經驗值增加20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHNJFD', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '特別課程', 'skill_description': '[等級上限 : 1]\r\n這是在楓之谷學院進行中的武公與艾畢奈亞的課程。', 'skill_level': 1, 'skill_effect': '增加攻擊BOSS怪物時傷害 20%\r\n無視怪物防禦率增加10%\r\n從怪物公園退場時獲得的經驗值增加20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHNJFD', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '特別課程', 'skill_description': '[等級上限 : 1]\r\n這是在楓之谷學院進行中的武公與艾畢奈亞的課程。', 'skill_level': 1, 'skill_effect': '增加攻擊BOSS怪物時傷害 20%\r\n無視怪物防禦率增加10%\r\n從怪物公園退場時獲得的經驗值增加20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHNJFD', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '特別課程', 'skill_description': '[等級上限 : 1]\r\n這是在楓之谷學院進行中的武公與艾畢奈亞的課程。', 'skill_level': 1, 'skill_effect': '增加攻擊BOSS怪物時傷害 15%\r\n無視怪物防禦率增加 10%\r\n從怪物公園退場時獲得的經驗值增加20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHNJFD', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '11702524'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '13002802'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '407.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '94.06'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44892'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '30'}, {'stat_name': 'STR', 'stat_value': '24241'}, {'stat_name': 'DEX', 'stat_value': '2792'}, {'stat_name': 'INT', 'stat_value': '1491'}, {'stat_name': 'LUK', 'stat_value': '1526'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '26359'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '70'}, {'stat_name': '攻擊速度', 'stat_value': '7'}, {'stat_name': '一般怪物傷害', 'stat_value': '12.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '35.00'}, {'stat_name': '攻擊力', 'stat_value': '2518'}, {'stat_name': '魔法攻擊力', 'stat_value': '712'}, {'stat_name': '戰鬥力', 'stat_value': '17771467'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
+          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '11702524'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '13002802'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '407.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '94.06'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44892'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神祕力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '30'}, {'stat_name': 'STR', 'stat_value': '24241'}, {'stat_name': 'DEX', 'stat_value': '2792'}, {'stat_name': 'INT', 'stat_value': '1491'}, {'stat_name': 'LUK', 'stat_value': '1526'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '26359'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '70'}, {'stat_name': '攻擊速度', 'stat_value': '7'}, {'stat_name': '一般怪物傷害', 'stat_value': '12.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '35.00'}, {'stat_name': '攻擊力', 'stat_value': '2518'}, {'stat_name': '魔法攻擊力', 'stat_value': '712'}, {'stat_name': '戰鬥力', 'stat_value': '17771467'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '特別課程', 'skill_description': '[等級上限 : 1]\r\n這是在楓之谷學院進行中的武公與艾畢奈亞的課程。', 'skill_level': 1, 'skill_effect': '增加攻擊BOSS怪物時傷害 15%\r\n無視怪物防禦率增加 10%\r\n從怪物公園退場時獲得的經驗值增加20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHNJFD', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '特別課程', 'skill_description': '[等級上限 : 1]\r\n這是在楓之谷學院進行中的武公與艾畢奈亞的課程。', 'skill_level': 1, 'skill_effect': '增加攻擊BOSS怪物時傷害 15%\r\n無視怪物防禦率增加 10%\r\n從怪物公園退場時獲得的經驗值增加 20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHNJFD', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[{'skill_name': '連接繩索', 'skill_description': '[等級上限 : 30]\r\n將鐵鍊拋向天空，快速移動。', 'skill_level': 19, 'skill_effect': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力19]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMA', 'skill_effect_next': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力20]'}, {'skill_name': '實用的時空門', 'skill_description': '[等級上限 : 30]\r\n形成可通往最近村莊的傳送點。門消失之前可以多次進出，在傳送點上按 ↑ 鍵移動。', 'skill_level': 10, 'skill_effect': '消耗100 HP，維持傳送點50秒\n冷卻時間為130秒\n[被動效果：全屬性增加2]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMB', 'skill_effect_next': '消耗100 HP，維持傳送點52秒\n冷卻時間為130秒\n[被動效果：全屬性增加3]'}, {'skill_name': '實用的會心之眼', 'skill_description': '[等級上限 : 30]\r\n賦予自己能找出敵人的弱點造成致命傷的能力。不能跟會心之眼重複使用。', 'skill_level': 25, 'skill_effect': '消耗HP 100，在255秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMC', 'skill_effect_next': '消耗HP 100，在258秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 6增加]'}, {'skill_name': '實用的神聖之火', 'skill_description': '[等級上限 : 30]\r\n最大HP與最大MP的量增加。不會與神聖之火重複使用。', 'skill_level': 21, 'skill_effect': '消耗HP 100，在243秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMD', 'skill_effect_next': '消耗HP 100，在246秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]'}, {'skill_name': '實用的戰鬥命令', 'skill_description': '[等級上限 : 30]\r\n一定時間內提升自身的所有技能等級。限於4轉技能可以增加到最大等級以上，其他技能只能提高到最大等級為止。\n部分例外的特別技能和初心者技能、戰鬥命令、實用的戰鬥命令、超技能、5轉、6轉技能的等級是無法提高技能等級。\n無法與戰鬥命令重複使用。', 'skill_level': 22, 'skill_effect': '消耗HP 100，在246秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBME', 'skill_effect_next': '消耗HP 100，在249秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]'}, {'skill_name': '實用的進階祝福', 'skill_description': '[等級上限 : 30]\r\n增加攻擊力、魔力、防禦力、最大HP、最大MP。\n祝福、進階祝福、實用的進階祝福中，僅套用較高數值的效果。', 'skill_level': 15, 'skill_effect': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加3]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMF', 'skill_effect_next': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加4]'}, {'skill_name': '實用的最終極速', 'skill_description': '[等級上限 : 30]\r\n使自己的攻擊速度額外增加1階段。最終極速和實用的最終極速中，僅套用較高數值的效果。', 'skill_level': 22, 'skill_effect': '攻擊速度增加1階段\n[被動效果：全屬性增加5]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMG', 'skill_effect_next': '攻擊速度增加1階段\n[被動效果：全屬性增加5]'}, {'skill_name': '瞬移', 'skill_description': '[等級上限 : 30]\r\n瞬間移動到地圖上隨機的位置。在空中按壓按鍵時，會在一定時間內漂浮且慢速移動來代替瞬間移動。', 'skill_level': 22, 'skill_effect': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 22增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMH', 'skill_effect_next': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 23增加]'}, {'skill_name': '艾爾達斯的新星', 'skill_description': '[等級上限 : 30]\r\n收集自己周圍的艾爾達斯後朝敵人引爆攻擊。被攻擊的敵人體內艾爾達紊亂，陷入無法行動狀態。\n艾爾達新星可在其他技能施放中使用，並可對攻擊無視與攻擊反射狀態的敵人造成傷害。', 'skill_level': 30, 'skill_effect': '消耗100 HP，對最多10名的敵人以330%的傷害攻擊5次，並進入無法行動狀態10秒\n依照利用艾爾達斯的超新星對敵人造成的傷害而增加無法行動的持續時間，最多增加100%\n冷卻時間 100秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMI', 'skill_effect_next': None}, {'skill_name': '艾爾達斯的意志', 'skill_description': '[等級上限 : 30]\r\n集中精神，以解除狀態異常。使用後，在3秒內對狀態異常免疫。但部分異常狀態效果不適用。\n艾爾達斯的意志在使用其他技能時仍可使用。', 'skill_level': 16, 'skill_effect': '消耗100 HP，冷卻時間400秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMJ', 'skill_effect_next': '消耗100 HP，冷卻時間395秒'}, {'skill_name': '實用的祈禱', 'skill_description': '[等級上限 : 30]\r\n一定時間內狩獵怪物時，可獲得更多的經驗值和道具。不能跟神聖祈禱重複使用。', 'skill_level': 19, 'skill_effect': '消耗HP 100，237秒間獲得經驗值增加29%，掉寶率增加20%\n冷卻時間 180秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBOA', 'skill_effect_next': '消耗HP 100，240秒間獲得經驗值增加30%，掉寶率增加20%\n冷卻時間 180秒'}, {'skill_name': '艾爾達斯的降臨', 'skill_description': '[等級上限 : 30]\r\n釋放濃縮的艾爾達攻擊周圍敵人。\n與方向鍵下同時使用時可召喚純淨艾爾達匯聚的物件艾爾達噴泉。\n使用自訂指令時可不輸入方向鍵僅以技能鍵召喚艾爾達噴泉。\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影侍從、祝雷、藍血、虛擬投影時，攻擊次數增加效果將改為相同效果的最終傷害增加。\n指令開關：滑鼠右鍵', 'skill_level': 18, 'skill_effect': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPG', 'skill_effect_next': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間'}, {'skill_name': '魔法迴路效能全開', 'skill_description': '[等級上限 : 30]\r\n魔力翅膀張開到最大將魔法迴路啟動到極限。', 'skill_level': 30, 'skill_effect': '消耗1000 MP，在60秒內，傷害增加45%\n使用攻擊技能時，每4秒額外消耗150MP，並發動魔力暴風最多對6名敵人造成1100%傷害攻擊3次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPH', 'skill_effect_next': None}, {'skill_name': '蜘蛛之鏡', 'skill_description': '[等級上限 : 30]\r\n利用威爾的艾爾達斯來崩壞空間，並把鏡面世界和現實世界連接後，把鏡面裡的蜘蛛具現在現實空間中。鏡面的蜘蛛攻擊處於反射狀態的敵人時，也不會使自己受傷。', 'skill_level': 1, 'skill_effect': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPJ', 'skill_effect_next': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒'}, {'skill_name': '格蘭蒂斯女神的祝福', 'skill_description': '[等級上限 : 30]\r\n依據不同種族展現相異樣貌的格蘭蒂斯女神，賜予與種族相符的祝福。受冷卻時間減少效果影響。', 'skill_level': 30, 'skill_effect': 'HP 100消耗，持續40秒\n超新星：使用技能時55%機率不受冷卻時間影響，最多6次不受影響\n傷害35%增加\n每個龍能球能量階段使凱撒的傷害追加增加11%\n雷普：將除武器外的裝備中，不使用屬性的攻擊力/魔力100%轉換為使用屬性。但不適用套裝效果，僅能轉換武器純攻擊力/魔力的150%為使用屬性\n攻擊力與魔力增加100\n阿尼瑪：傷害增加40%\n虎影的符籍與卷軸道力補充量增加75%，菈菈在龍脈迴響觸發時最終傷害增幅為11%，蓮的梅花劍絕技、亡魂劍絕技、蒼龍破天劍的最終傷害增加15%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBIG', 'skill_effect_next': None}, {'skill_name': '烈陽印記', 'skill_description': '[等級上限 : 30]\r\n利用米特拉的力量釋出太陽的熱氣後，具現出火焰的憤怒。火焰的紋樣即使對反射攻擊狀態的敵人進行攻擊也不會受到傷害。', 'skill_level': 2, 'skill_effect': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBJJ', 'skill_effect_next': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒'}, {'skill_name': '實用的神聖之泉', 'skill_description': '[等級上限 : 30]\r\n召喚神聖的噴泉，用神聖的力量恢復隊員的HP。不死狀態的隊員也可使用，靠近噴泉並按下向上方向鍵即可回復HP。\n包含自身在內的隊員所使用的神聖之泉及實用的神聖之泉，在地圖內只能存在一個。\n實用的神聖之泉在持續時間結束前消失時，會留下神聖之痕。在存在神聖之泉以及除自身外隊員的實用的神聖之泉及神聖之痕的地圖中無法使用。\n不受再使用冷卻時間重置、回復技能效率增加、增加召喚獸持續時間效果影響，且無法在傳送點附近召喚。', 'skill_level': 19, 'skill_effect': '消耗100 HP，持續49秒。使用時將恢復20%HP，共可使用14次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為71秒\n[被動效果：全屬性增加4]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBFH', 'skill_effect_next': '消耗100 HP，持續50秒。使用時將恢復25%HP，共可使用15次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為70秒\n[被動效果：全屬性增加4]'}, {'skill_name': '行星強化', 'skill_description': '[等級上限 : 60]\r\n強化行星。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '行星的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIG', 'skill_effect_next': None}, {'skill_name': '碎片/奇蹟強化', 'skill_description': '[等級上限 : 60]\r\n強化碎片/奇蹟。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '碎片/奇蹟的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAII', 'skill_effect_next': None}, {'skill_name': '閃擊強化', 'skill_description': '[等級上限 : 60]\r\n強化閃擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '閃擊的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIH', 'skill_effect_next': None}, {'skill_name': '刺擊強化', 'skill_description': '[等級上限 : 60]\r\n強化刺擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '刺擊的最終傷害增加300%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJA', 'skill_effect_next': None}, {'skill_name': '穿刺強化', 'skill_description': '[等級上限 : 60]\r\n強化穿刺。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '穿刺的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJC', 'skill_effect_next': None}, {'skill_name': '魔劍共鳴強化', 'skill_description': '[等級上限 : 60]\r\n強化魔劍共鳴。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔劍共鳴的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJD', 'skill_effect_next': None}, {'skill_name': '創造強化', 'skill_description': '[等級上限 : 60]\r\n強化創造。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '創造的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJF', 'skill_effect_next': None}, {'skill_name': '十字斬強化', 'skill_description': '[等級上限 : 60]\r\n強化十字斬。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '十字斬的最終傷害增加180%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJB', 'skill_effect_next': None}, {'skill_name': '追蹤強化', 'skill_description': '[等級上限 : 60]\r\n強化追蹤。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '追蹤的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKA', 'skill_effect_next': None}, {'skill_name': '回歸強化', 'skill_description': '[等級上限 : 60]\r\n強化回歸。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率強化20%', 'skill_level': 60, 'skill_effect': '回歸的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJG', 'skill_effect_next': None}, {'skill_name': '劍域強化', 'skill_description': '[等級上限 : 60]\r\n強化劍域。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '劍域的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJH', 'skill_effect_next': None}, {'skill_name': '切割強化', 'skill_description': '[等級上限 : 60]\r\n強化切割。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '切割的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJJ', 'skill_effect_next': None}, {'skill_name': '綻放強化', 'skill_description': '[等級上限 : 60]\r\n強化綻放。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '綻放的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKC', 'skill_effect_next': None}, {'skill_name': '死亡標記強化', 'skill_description': '[等級上限 : 60]\r\n強化死亡標記。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '死亡標記的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKB', 'skill_effect_next': None}, {'skill_name': '踐踏強化', 'skill_description': '[等級上限 : 60]\r\n強化踐踏。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '踐踏的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJI', 'skill_effect_next': None}, {'skill_name': '狂風強化', 'skill_description': '[等級上限 : 60]\r\n強化狂風。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '狂風的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKD', 'skill_effect_next': None}, {'skill_name': '魔力爆裂強化', 'skill_description': '[等級上限 : 60]\r\n強化魔力爆裂。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔力爆裂的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJE', 'skill_effect_next': None}, {'skill_name': '幻靈武具', 'skill_description': '[等級上限 : 30]\r\n將部分生命力賦予武器，發揮強大的力量。', 'skill_level': 30, 'skill_effect': '消耗100 HP，130秒內無視怪物防禦率 16%，最終傷害值增加6% 。\n每5秒使用自己的攻擊技能時，發射鬥氣波動攻擊敵人，最多對10名敵人造成1100%傷害6次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBMA', 'skill_effect_next': None}, {'skill_name': '鋼鐵之軀', 'skill_description': '[等級上限 : 30]\r\n肉體變成和鋼鐵一樣，不會受敵人的攻擊彈開。', 'skill_level': 30, 'skill_effect': '消耗100 HP，在18秒內，不會被任何攻擊擊退，並提升狀態異常抗性80\n冷卻時間120秒\n[被動效果：力量增加30、最大HP增加1500]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBKG', 'skill_effect_next': None}, {'skill_name': '毀滅', 'skill_description': '[等級上限 : 30]\r\n召喚古代滅亡之劍讓四周崩毀。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害。', 'skill_level': 30, 'skill_effect': '消耗MP1000，最多攻擊15名敵人\n召喚後，發動以1012%傷害攻擊6次的攻擊12次\n召喚後插上劍，發動以1485%傷害攻擊9次的攻擊8次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMF', 'skill_effect_next': None}, {'skill_name': '無限', 'skill_description': '[等級上限 : 30]\r\n創造一個空間，讓無數的乙太之劍生成。乙太之劍只會在阿戴爾附近追擊敵人，當劍和阿戴爾之間的距離變遠，劍會移動到阿戴爾附近追擊新敵人。\n以無限指令創造出來的乙太之劍會進行回歸；不套用爆裂，只套用死亡標記。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害，只有在阿戴爾處於戰鬥狀態時才會追擊敵人。\r\n所需技能：死亡標記 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP1000，在進行施展及解除動作時無敵\n存在20秒，創造18把乙太之劍，可以770%傷害攻擊2次\n攻擊命中時以5%機率形成乙太結晶\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMI', 'skill_effect_next': None}, {'skill_name': '復原', 'skill_description': '[等級上限 : 30]\r\n暫時修復燒焦的魔力迴路，讓過去的魔力之翼復活。\n復原的攻擊可無視打擊，並且可對反射攻勢狀態的敵人造成傷害，再次使用技能時會立刻消失。\r\n所需技能：高潔精神 10等級以上', 'skill_level': 30, 'skill_effect': '施放及施放後，每秒消耗最大MP的2%\n20秒內，傷害增加45%、乙太獲得量增加80%、可聽從追蹤命令的乙太之劍增加2把。施展時，無論持有多少乙太之劍，立即命令2把乙太之劍\n每隔一定時間展開魔力翅膀，最多對6名敵人造成1980%傷害攻擊3次，恢復包含自身在內的隊員最大HP的10.5%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMJ', 'skill_effect_next': None}, {'skill_name': '乙太風暴', 'skill_description': '[等級上限 : 30]\r\n讓下達追蹤命令的所有乙太之劍在自身周圍有如暴風般地移動。以追蹤追擊敵人的乙太之劍數量比例，在自身周圍產生幻影移動。暴風攻擊即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。再次使用技能時可立即結束。\r\n所需技能：回歸 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP500，14秒內每隔一段時間會最多向7名敵人以869%傷害自動攻擊2次\n施展時下達命令的乙太之劍每超出1雙，攻擊次數增加2次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAPG', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '連接繩索', 'skill_description': '[等級上限 : 30]\r\n將鐵鍊拋向天空，快速移動。', 'skill_level': 19, 'skill_effect': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力19]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMA', 'skill_effect_next': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力20]'}, {'skill_name': '實用的時空門', 'skill_description': '[等級上限 : 30]\r\n形成可通往最近村莊的傳送點。門消失之前可以多次進出，在傳送點上按 ↑ 鍵移動。', 'skill_level': 10, 'skill_effect': '消耗100 HP，維持傳送點50秒\n冷卻時間為130秒\n[被動效果：全屬性增加2]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMB', 'skill_effect_next': '消耗100 HP，維持傳送點52秒\n冷卻時間為130秒\n[被動效果：全屬性增加3]'}, {'skill_name': '實用的會心之眼', 'skill_description': '[等級上限 : 30]\r\n賦予自己能找出敵人的弱點造成致命傷的能力。不能跟會心之眼重複使用。', 'skill_level': 25, 'skill_effect': '消耗HP 100，在255秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMC', 'skill_effect_next': '消耗HP 100，在258秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 6增加]'}, {'skill_name': '實用的神聖之火', 'skill_description': '[等級上限 : 30]\r\n最大HP與最大MP的量增加。不會與神聖之火重複使用。', 'skill_level': 21, 'skill_effect': '消耗HP 100，在243秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMD', 'skill_effect_next': '消耗HP 100，在246秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]'}, {'skill_name': '實用的戰鬥命令', 'skill_description': '[等級上限 : 30]\r\n一定時間內提升自身的所有技能等級。限於4轉技能可以增加到最大等級以上，其他技能只能提高到最大等級為止。\n部分例外的特別技能和初心者技能、戰鬥命令、實用的戰鬥命令、超技能、5轉、6轉技能的等級是無法提高技能等級。\n無法與戰鬥命令重複使用。', 'skill_level': 22, 'skill_effect': '消耗HP 100，在246秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBME', 'skill_effect_next': '消耗HP 100，在249秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]'}, {'skill_name': '實用的進階祝福', 'skill_description': '[等級上限 : 30]\r\n增加攻擊力、魔力、防禦力、最大HP、最大MP。\n祝福、進階祝福、實用的進階祝福中，僅套用較高數值的效果。', 'skill_level': 15, 'skill_effect': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加3]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMF', 'skill_effect_next': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加4]'}, {'skill_name': '實用的最終極速', 'skill_description': '[等級上限 : 30]\r\n使自己的攻擊速度額外增加1階段。最終極速和實用的最終極速中，僅套用較高數值的效果。', 'skill_level': 22, 'skill_effect': '攻擊速度增加1階段\n[被動效果：全屬性增加5]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMG', 'skill_effect_next': '攻擊速度增加1階段\n[被動效果：全屬性增加5]'}, {'skill_name': '瞬移', 'skill_description': '[等級上限 : 30]\r\n瞬間移動到地圖上隨機的位置。在空中按壓按鍵時，會在一定時間內漂浮且慢速移動來代替瞬間移動。', 'skill_level': 22, 'skill_effect': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 22增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMH', 'skill_effect_next': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 23增加]'}, {'skill_name': '艾爾達斯的新星', 'skill_description': '[等級上限 : 30]\r\n收集自己周圍的艾爾達斯後朝敵人引爆攻擊。被攻擊的敵人體內艾爾達紊亂，陷入無法行動狀態。\n艾爾達新星可在其他技能施放中使用，並可對攻擊無視與攻擊反射狀態的敵人造成傷害。', 'skill_level': 30, 'skill_effect': '消耗100 HP，對最多10名的敵人以330%的傷害攻擊5次，並進入無法行動狀態10秒\n依照利用艾爾達斯的超新星對敵人造成的傷害而增加無法行動的持續時間，最多增加100%\n冷卻時間 100秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMI', 'skill_effect_next': None}, {'skill_name': '艾爾達斯的意志', 'skill_description': '[等級上限 : 30]\r\n集中精神，以解除狀態異常。使用後，在3秒內對狀態異常免疫。但部分異常狀態效果不適用。\n艾爾達斯的意志在使用其他技能時仍可使用。', 'skill_level': 16, 'skill_effect': '消耗100 HP，冷卻時間400秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMJ', 'skill_effect_next': '消耗100 HP，冷卻時間395秒'}, {'skill_name': '實用的祈禱', 'skill_description': '[等級上限 : 30]\r\n一定時間內狩獵怪物時，可獲得更多的經驗值和道具。不能跟神聖祈禱重複使用。', 'skill_level': 19, 'skill_effect': '消耗HP 100，237秒間獲得經驗值增加29%，掉寶率增加20%\n冷卻時間 180秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBOA', 'skill_effect_next': '消耗HP 100，240秒間獲得經驗值增加30%，掉寶率增加20%\n冷卻時間 180秒'}, {'skill_name': '艾爾達斯的降臨', 'skill_description': '[等級上限 : 30]\r\n釋放濃縮的艾爾達攻擊周圍敵人。\n與方向鍵下同時使用時可召喚純淨艾爾達匯聚的物件艾爾達斯噴泉。\n使用自訂指令時可不輸入方向鍵僅以技能鍵召喚艾爾達噴泉。\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影侍從、祝雷、藍血、虛擬投影時，攻擊次數增加效果將改為相同效果的最終傷害增加。\n指令開關：滑鼠右鍵', 'skill_level': 18, 'skill_effect': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPG', 'skill_effect_next': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間'}, {'skill_name': '魔法迴路效能全開', 'skill_description': '[等級上限 : 30]\r\n魔力翅膀張開到最大將魔法迴路啟動到極限。', 'skill_level': 30, 'skill_effect': '消耗1000 MP，在60秒內，傷害增加45%\n使用攻擊技能時，每4秒額外消耗150MP，並發動魔力暴風最多對6名敵人造成1100%傷害攻擊3次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPH', 'skill_effect_next': None}, {'skill_name': '蜘蛛之鏡', 'skill_description': '[等級上限 : 30]\r\n利用威爾的艾爾達斯來崩壞空間，並把鏡面世界和現實世界連接後，把鏡面裡的蜘蛛具現在現實空間中。鏡面的蜘蛛攻擊處於反射狀態的敵人時，也不會使自己受傷。', 'skill_level': 1, 'skill_effect': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPJ', 'skill_effect_next': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒'}, {'skill_name': '格蘭蒂斯女神的祝福', 'skill_description': '[等級上限 : 30]\r\n依據不同種族展現相異樣貌的格蘭蒂斯女神，賜予與種族相符的祝福。受冷卻時間減少效果影響。', 'skill_level': 30, 'skill_effect': 'HP 100消耗，持續40秒\n超新星：使用技能時55%機率不受冷卻時間影響，最多6次不受影響\n傷害35%增加\n每個龍能球能量階段使凱撒的傷害追加增加11%\n雷普：將除武器外的裝備中，不使用屬性的攻擊力/魔力100%轉換為使用屬性。但不適用套裝效果，僅能轉換武器純攻擊力/魔力的150%為使用屬性\n攻擊力與魔力增加100\n阿尼瑪：傷害增加40%\n虎影的符籍與卷軸道力補充量增加75%，菈菈在龍脈迴響觸發時最終傷害增幅為11%，蓮的梅花劍絕技、亡魂劍絕技、蒼龍破天劍的最終傷害增加15%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBIG', 'skill_effect_next': None}, {'skill_name': '烈陽印記', 'skill_description': '[等級上限 : 30]\r\n利用米特拉的力量釋出太陽的熱氣後，具現出火焰的憤怒。火焰的紋樣即使對反射攻擊狀態的敵人進行攻擊也不會受到傷害。', 'skill_level': 2, 'skill_effect': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBJJ', 'skill_effect_next': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒'}, {'skill_name': '實用的神聖之泉', 'skill_description': '[等級上限 : 30]\r\n召喚神聖的噴泉，用神聖的力量恢復隊員的HP。不死狀態的隊員也可使用，靠近噴泉並按下向上方向鍵即可回復HP。\n包含自身在內的隊員所使用的神聖之泉及實用的神聖之泉，在地圖內只能存在一個。\n實用的神聖之泉在持續時間結束前消失時，會留下神聖之痕。在存在神聖之泉以及除自身外隊員的實用的神聖之泉及神聖之痕的地圖中無法使用。\n不受再使用冷卻時間重置、回復技能效率增加、增加召喚獸持續時間效果影響，且無法在傳送點附近召喚。', 'skill_level': 19, 'skill_effect': '消耗100 HP，持續49秒。使用時將恢復20%HP，共可使用14次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為71秒\n[被動效果：全屬性增加4]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBFH', 'skill_effect_next': '消耗100 HP，持續50秒。使用時將恢復25%HP，共可使用15次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為70秒\n[被動效果：全屬性增加4]'}, {'skill_name': '行星強化', 'skill_description': '[等級上限 : 60]\r\n強化行星。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '行星的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIG', 'skill_effect_next': None}, {'skill_name': '碎片/奇蹟強化', 'skill_description': '[等級上限 : 60]\r\n強化碎片/奇蹟。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '碎片/奇蹟的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAII', 'skill_effect_next': None}, {'skill_name': '閃擊強化', 'skill_description': '[等級上限 : 60]\r\n強化閃擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '閃擊的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIH', 'skill_effect_next': None}, {'skill_name': '刺擊強化', 'skill_description': '[等級上限 : 60]\r\n強化刺擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '刺擊的最終傷害增加300%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJA', 'skill_effect_next': None}, {'skill_name': '穿刺強化', 'skill_description': '[等級上限 : 60]\r\n強化穿刺。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '穿刺的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJC', 'skill_effect_next': None}, {'skill_name': '魔劍共鳴強化', 'skill_description': '[等級上限 : 60]\r\n強化魔劍共鳴。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔劍共鳴的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJD', 'skill_effect_next': None}, {'skill_name': '創造強化', 'skill_description': '[等級上限 : 60]\r\n強化創造。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '創造的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJF', 'skill_effect_next': None}, {'skill_name': '十字斬強化', 'skill_description': '[等級上限 : 60]\r\n強化十字斬。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '十字斬的最終傷害增加180%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJB', 'skill_effect_next': None}, {'skill_name': '追蹤強化', 'skill_description': '[等級上限 : 60]\r\n強化追蹤。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '追蹤的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKA', 'skill_effect_next': None}, {'skill_name': '回歸強化', 'skill_description': '[等級上限 : 60]\r\n強化回歸。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率強化20%', 'skill_level': 60, 'skill_effect': '回歸的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJG', 'skill_effect_next': None}, {'skill_name': '劍域強化', 'skill_description': '[等級上限 : 60]\r\n強化劍域。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '劍域的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJH', 'skill_effect_next': None}, {'skill_name': '切割強化', 'skill_description': '[等級上限 : 60]\r\n強化切割。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '切割的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJJ', 'skill_effect_next': None}, {'skill_name': '綻放強化', 'skill_description': '[等級上限 : 60]\r\n強化綻放。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '綻放的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKC', 'skill_effect_next': None}, {'skill_name': '死亡標記強化', 'skill_description': '[等級上限 : 60]\r\n強化死亡標記。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '死亡標記的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKB', 'skill_effect_next': None}, {'skill_name': '踐踏強化', 'skill_description': '[等級上限 : 60]\r\n強化踐踏。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '踐踏的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJI', 'skill_effect_next': None}, {'skill_name': '狂風強化', 'skill_description': '[等級上限 : 60]\r\n強化狂風。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '狂風的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKD', 'skill_effect_next': None}, {'skill_name': '魔力爆裂強化', 'skill_description': '[等級上限 : 60]\r\n強化魔力爆裂。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔力爆裂的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJE', 'skill_effect_next': None}, {'skill_name': '幻靈武具', 'skill_description': '[等級上限 : 30]\r\n將部分生命力賦予武器，發揮強大的力量。', 'skill_level': 30, 'skill_effect': '消耗100 HP，130秒內無視怪物防禦率 16%，最終傷害值增加6% 。\n每5秒使用自己的攻擊技能時，發射鬥氣波動攻擊敵人，最多對10名敵人造成1100%傷害6次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBMA', 'skill_effect_next': None}, {'skill_name': '鋼鐵之軀', 'skill_description': '[等級上限 : 30]\r\n肉體變成和鋼鐵一樣，不會受敵人的攻擊彈開。', 'skill_level': 30, 'skill_effect': '消耗100 HP，在18秒內，不會被任何攻擊擊退，並提升狀態異常抗性80\n冷卻時間120秒\n[被動效果：力量增加30、最大HP增加1500]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBKG', 'skill_effect_next': None}, {'skill_name': '毀滅', 'skill_description': '[等級上限 : 30]\r\n召喚古代滅亡之劍讓四周崩毀。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害。', 'skill_level': 30, 'skill_effect': '消耗MP1000，最多攻擊15名敵人\n召喚後，發動以1012%傷害攻擊6次的攻擊12次\n召喚後插上劍，發動以1485%傷害攻擊9次的攻擊8次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMF', 'skill_effect_next': None}, {'skill_name': '無限', 'skill_description': '[等級上限 : 30]\r\n創造一個空間，讓無數的乙太之劍生成。乙太之劍只會在阿戴爾附近追擊敵人，當劍和阿戴爾之間的距離變遠，劍會移動到阿戴爾附近追擊新敵人。\n以無限指令創造出來的乙太之劍會進行回歸；不套用爆裂，只套用死亡標記。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害，只有在阿戴爾處於戰鬥狀態時才會追擊敵人。\r\n所需技能：死亡標記 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP1000，在進行施展及解除動作時無敵\n存在20秒，創造18把乙太之劍，可以770%傷害攻擊2次\n攻擊命中時以5%機率形成乙太結晶\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMI', 'skill_effect_next': None}, {'skill_name': '復原', 'skill_description': '[等級上限 : 30]\r\n暫時修復燒焦的魔力迴路，讓過去的魔力之翼復活。\n復原的攻擊可無視打擊，並且可對反射攻勢狀態的敵人造成傷害，再次使用技能時會立刻消失。\r\n所需技能：高潔精神 10等級以上', 'skill_level': 30, 'skill_effect': '施放及施放後，每秒消耗最大MP的2%\n20秒內，傷害增加45%、乙太獲得量增加80%、可聽從追蹤命令的乙太之劍增加2把。施展時，無論持有多少乙太之劍，立即命令2把乙太之劍\n每隔一定時間展開魔力翅膀，最多對6名敵人造成1980%傷害攻擊3次，恢復包含自身在內的隊員最大HP的10.5%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMJ', 'skill_effect_next': None}, {'skill_name': '乙太風暴', 'skill_description': '[等級上限 : 30]\r\n讓下達追蹤命令的所有乙太之劍在自身周圍有如暴風般地移動。以追蹤追擊敵人的乙太之劍數量比例，在自身周圍產生幻影移動。暴風攻擊即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。再次使用技能時可立即結束。\r\n所需技能：回歸 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP500，14秒內每隔一段時間會最多向7名敵人以869%傷害自動攻擊2次\n施展時下達命令的乙太之劍每超出1雙，攻擊次數增加2次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAPG', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,6 +606,11 @@
           <t>remain_ap</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mentorship_stat</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -621,6 +626,11 @@
       </c>
       <c r="D2" t="n">
         <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
   </sheetData>
